--- a/Docs/03_Product_Master.xlsx
+++ b/Docs/03_Product_Master.xlsx
@@ -1,37 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbnsi\OneDrive\Documents\GitHub\Rice-Spice-Hub-Ver.-1.0\Docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Category Code</t>
+  </si>
+  <si>
+    <t>Subcategory Code</t>
+  </si>
+  <si>
+    <t>Weight/Size</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Featured</t>
+  </si>
+  <si>
+    <t>Badge</t>
+  </si>
+  <si>
+    <t>Tax Included</t>
+  </si>
+  <si>
+    <t>Free Delivery</t>
+  </si>
+  <si>
+    <t>Sort Order</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +114,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,74 +417,64 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Product ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Product Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Category Code</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Subcategory Code</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Weight/Size</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sale Price</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Docs/03_Product_Master.xlsx
+++ b/Docs/03_Product_Master.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>Product ID</t>
   </si>
@@ -73,6 +73,39 @@
   </si>
   <si>
     <t>Sort Order</t>
+  </si>
+  <si>
+    <t>AAA0001</t>
+  </si>
+  <si>
+    <t>India Gate Basmati Rice</t>
+  </si>
+  <si>
+    <t>India Gate</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>AAA0002</t>
+  </si>
+  <si>
+    <t>Daawat Basmati Rice</t>
+  </si>
+  <si>
+    <t>Daawat</t>
+  </si>
+  <si>
+    <t>AAA0003</t>
+  </si>
+  <si>
+    <t>Tilda Basmati Rice</t>
+  </si>
+  <si>
+    <t>Tilda</t>
   </si>
 </sst>
 </file>
@@ -113,9 +146,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,8 +454,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -475,6 +515,75 @@
       </c>
       <c r="R1" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>980</v>
       </c>
     </row>
   </sheetData>
